--- a/data/clinic/data.xlsx
+++ b/data/clinic/data.xlsx
@@ -454,7 +454,7 @@
         <v>高松市国民健康保険女木診療所</v>
       </c>
       <c r="E2" t="str">
-        <v>オーテがみまもるクリニック</v>
+        <v/>
       </c>
       <c r="F2" t="str">
         <v>高松市女木町112</v>
@@ -495,7 +495,7 @@
         <v>高松市国民健康保険男木診療所</v>
       </c>
       <c r="E3" t="str">
-        <v>SETOLAS　男木島診療所</v>
+        <v/>
       </c>
       <c r="F3" t="str">
         <v>高松市男木町1988</v>
